--- a/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E3C105-4F21-4147-A553-18BC959AB272}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB468191-3C32-4C81-BA54-AAFFF479EA80}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{299BED95-B46B-40BA-B1E8-90B03A19110E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A99117C-78D4-4CC6-9D46-00758AC52435}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A72E5B68-BEF2-4C71-A21F-5B274702A020}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98070562-FDAE-451A-863A-FA05E4E017ED}"/>
 </file>